--- a/00_索引与规范/标准索引_Standards_Index_v3_20260615.xlsx
+++ b/00_索引与规范/标准索引_Standards_Index_v3_20260615.xlsx
@@ -178,7 +178,7 @@
       </patternFill>
     </fill>
   </fills>
-  <borders count="2">
+  <borders count="6">
     <border>
       <left/>
       <right/>
@@ -200,11 +200,55 @@
         <color rgb="00B4C6E7"/>
       </bottom>
     </border>
+    <border>
+      <left/>
+      <right/>
+      <top style="thin">
+        <color rgb="00B4C6E7"/>
+      </top>
+      <bottom/>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right style="thin">
+        <color rgb="00B4C6E7"/>
+      </right>
+      <top style="thin">
+        <color rgb="00B4C6E7"/>
+      </top>
+      <bottom/>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right/>
+      <top style="thin">
+        <color rgb="00B4C6E7"/>
+      </top>
+      <bottom style="thin">
+        <color rgb="00B4C6E7"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right style="thin">
+        <color rgb="00B4C6E7"/>
+      </right>
+      <top style="thin">
+        <color rgb="00B4C6E7"/>
+      </top>
+      <bottom style="thin">
+        <color rgb="00B4C6E7"/>
+      </bottom>
+      <diagonal/>
+    </border>
   </borders>
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="36">
+  <cellXfs count="38">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
@@ -277,6 +321,8 @@
       <alignment horizontal="left" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="15" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="4" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="5" pivotButton="0" quotePrefix="0" xfId="0"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0" hidden="0"/>
@@ -662,7 +708,7 @@
     <row r="3">
       <c r="B3" s="2" t="inlineStr">
         <is>
-          <t>v3.0 FINAL | 2026-06-15 | 第一性原理 + 丰田5S 整理 | 维护: LEISA.COM 技术部</t>
+          <t>v3.0 FINAL | 2026-06-15 | 第一性原理 + 丰田5S 整理 | 技术部维护</t>
         </is>
       </c>
     </row>
@@ -4395,20 +4441,20 @@
           <t>▌FRP管-高压 (6 项)</t>
         </is>
       </c>
-      <c r="B2" s="19" t="n"/>
-      <c r="C2" s="19" t="n"/>
-      <c r="D2" s="19" t="n"/>
-      <c r="E2" s="19" t="n"/>
-      <c r="F2" s="19" t="n"/>
-      <c r="G2" s="19" t="n"/>
-      <c r="H2" s="19" t="n"/>
-      <c r="I2" s="19" t="n"/>
-      <c r="J2" s="19" t="n"/>
-      <c r="K2" s="19" t="n"/>
-      <c r="L2" s="19" t="n"/>
-      <c r="M2" s="19" t="n"/>
-      <c r="N2" s="19" t="n"/>
-      <c r="O2" s="19" t="n"/>
+      <c r="B2" s="36" t="n"/>
+      <c r="C2" s="36" t="n"/>
+      <c r="D2" s="36" t="n"/>
+      <c r="E2" s="36" t="n"/>
+      <c r="F2" s="36" t="n"/>
+      <c r="G2" s="36" t="n"/>
+      <c r="H2" s="36" t="n"/>
+      <c r="I2" s="36" t="n"/>
+      <c r="J2" s="36" t="n"/>
+      <c r="K2" s="36" t="n"/>
+      <c r="L2" s="36" t="n"/>
+      <c r="M2" s="36" t="n"/>
+      <c r="N2" s="36" t="n"/>
+      <c r="O2" s="37" t="n"/>
     </row>
     <row r="3">
       <c r="A3" s="14" t="n">
@@ -4838,20 +4884,20 @@
           <t>▌FRP管-低压 (3 项)</t>
         </is>
       </c>
-      <c r="B10" s="19" t="n"/>
-      <c r="C10" s="19" t="n"/>
-      <c r="D10" s="19" t="n"/>
-      <c r="E10" s="19" t="n"/>
-      <c r="F10" s="19" t="n"/>
-      <c r="G10" s="19" t="n"/>
-      <c r="H10" s="19" t="n"/>
-      <c r="I10" s="19" t="n"/>
-      <c r="J10" s="19" t="n"/>
-      <c r="K10" s="19" t="n"/>
-      <c r="L10" s="19" t="n"/>
-      <c r="M10" s="19" t="n"/>
-      <c r="N10" s="19" t="n"/>
-      <c r="O10" s="19" t="n"/>
+      <c r="B10" s="36" t="n"/>
+      <c r="C10" s="36" t="n"/>
+      <c r="D10" s="36" t="n"/>
+      <c r="E10" s="36" t="n"/>
+      <c r="F10" s="36" t="n"/>
+      <c r="G10" s="36" t="n"/>
+      <c r="H10" s="36" t="n"/>
+      <c r="I10" s="36" t="n"/>
+      <c r="J10" s="36" t="n"/>
+      <c r="K10" s="36" t="n"/>
+      <c r="L10" s="36" t="n"/>
+      <c r="M10" s="36" t="n"/>
+      <c r="N10" s="36" t="n"/>
+      <c r="O10" s="37" t="n"/>
     </row>
     <row r="11">
       <c r="A11" s="14" t="n">
@@ -5074,20 +5120,20 @@
           <t>▌FRP管-通用 (20 项)</t>
         </is>
       </c>
-      <c r="B15" s="19" t="n"/>
-      <c r="C15" s="19" t="n"/>
-      <c r="D15" s="19" t="n"/>
-      <c r="E15" s="19" t="n"/>
-      <c r="F15" s="19" t="n"/>
-      <c r="G15" s="19" t="n"/>
-      <c r="H15" s="19" t="n"/>
-      <c r="I15" s="19" t="n"/>
-      <c r="J15" s="19" t="n"/>
-      <c r="K15" s="19" t="n"/>
-      <c r="L15" s="19" t="n"/>
-      <c r="M15" s="19" t="n"/>
-      <c r="N15" s="19" t="n"/>
-      <c r="O15" s="19" t="n"/>
+      <c r="B15" s="36" t="n"/>
+      <c r="C15" s="36" t="n"/>
+      <c r="D15" s="36" t="n"/>
+      <c r="E15" s="36" t="n"/>
+      <c r="F15" s="36" t="n"/>
+      <c r="G15" s="36" t="n"/>
+      <c r="H15" s="36" t="n"/>
+      <c r="I15" s="36" t="n"/>
+      <c r="J15" s="36" t="n"/>
+      <c r="K15" s="36" t="n"/>
+      <c r="L15" s="36" t="n"/>
+      <c r="M15" s="36" t="n"/>
+      <c r="N15" s="36" t="n"/>
+      <c r="O15" s="37" t="n"/>
     </row>
     <row r="16">
       <c r="A16" s="14" t="n">
@@ -6467,20 +6513,20 @@
           <t>▌柔性复合管 (4 项)</t>
         </is>
       </c>
-      <c r="B37" s="19" t="n"/>
-      <c r="C37" s="19" t="n"/>
-      <c r="D37" s="19" t="n"/>
-      <c r="E37" s="19" t="n"/>
-      <c r="F37" s="19" t="n"/>
-      <c r="G37" s="19" t="n"/>
-      <c r="H37" s="19" t="n"/>
-      <c r="I37" s="19" t="n"/>
-      <c r="J37" s="19" t="n"/>
-      <c r="K37" s="19" t="n"/>
-      <c r="L37" s="19" t="n"/>
-      <c r="M37" s="19" t="n"/>
-      <c r="N37" s="19" t="n"/>
-      <c r="O37" s="19" t="n"/>
+      <c r="B37" s="36" t="n"/>
+      <c r="C37" s="36" t="n"/>
+      <c r="D37" s="36" t="n"/>
+      <c r="E37" s="36" t="n"/>
+      <c r="F37" s="36" t="n"/>
+      <c r="G37" s="36" t="n"/>
+      <c r="H37" s="36" t="n"/>
+      <c r="I37" s="36" t="n"/>
+      <c r="J37" s="36" t="n"/>
+      <c r="K37" s="36" t="n"/>
+      <c r="L37" s="36" t="n"/>
+      <c r="M37" s="36" t="n"/>
+      <c r="N37" s="36" t="n"/>
+      <c r="O37" s="37" t="n"/>
     </row>
     <row r="38">
       <c r="A38" s="14" t="n">
@@ -6752,20 +6798,20 @@
           <t>▌金属管-油套管 (3 项)</t>
         </is>
       </c>
-      <c r="B43" s="19" t="n"/>
-      <c r="C43" s="19" t="n"/>
-      <c r="D43" s="19" t="n"/>
-      <c r="E43" s="19" t="n"/>
-      <c r="F43" s="19" t="n"/>
-      <c r="G43" s="19" t="n"/>
-      <c r="H43" s="19" t="n"/>
-      <c r="I43" s="19" t="n"/>
-      <c r="J43" s="19" t="n"/>
-      <c r="K43" s="19" t="n"/>
-      <c r="L43" s="19" t="n"/>
-      <c r="M43" s="19" t="n"/>
-      <c r="N43" s="19" t="n"/>
-      <c r="O43" s="19" t="n"/>
+      <c r="B43" s="36" t="n"/>
+      <c r="C43" s="36" t="n"/>
+      <c r="D43" s="36" t="n"/>
+      <c r="E43" s="36" t="n"/>
+      <c r="F43" s="36" t="n"/>
+      <c r="G43" s="36" t="n"/>
+      <c r="H43" s="36" t="n"/>
+      <c r="I43" s="36" t="n"/>
+      <c r="J43" s="36" t="n"/>
+      <c r="K43" s="36" t="n"/>
+      <c r="L43" s="36" t="n"/>
+      <c r="M43" s="36" t="n"/>
+      <c r="N43" s="36" t="n"/>
+      <c r="O43" s="37" t="n"/>
     </row>
     <row r="44">
       <c r="A44" s="14" t="n">
@@ -6976,20 +7022,20 @@
           <t>▌金属材料-通用 (3 项)</t>
         </is>
       </c>
-      <c r="B48" s="19" t="n"/>
-      <c r="C48" s="19" t="n"/>
-      <c r="D48" s="19" t="n"/>
-      <c r="E48" s="19" t="n"/>
-      <c r="F48" s="19" t="n"/>
-      <c r="G48" s="19" t="n"/>
-      <c r="H48" s="19" t="n"/>
-      <c r="I48" s="19" t="n"/>
-      <c r="J48" s="19" t="n"/>
-      <c r="K48" s="19" t="n"/>
-      <c r="L48" s="19" t="n"/>
-      <c r="M48" s="19" t="n"/>
-      <c r="N48" s="19" t="n"/>
-      <c r="O48" s="19" t="n"/>
+      <c r="B48" s="36" t="n"/>
+      <c r="C48" s="36" t="n"/>
+      <c r="D48" s="36" t="n"/>
+      <c r="E48" s="36" t="n"/>
+      <c r="F48" s="36" t="n"/>
+      <c r="G48" s="36" t="n"/>
+      <c r="H48" s="36" t="n"/>
+      <c r="I48" s="36" t="n"/>
+      <c r="J48" s="36" t="n"/>
+      <c r="K48" s="36" t="n"/>
+      <c r="L48" s="36" t="n"/>
+      <c r="M48" s="36" t="n"/>
+      <c r="N48" s="36" t="n"/>
+      <c r="O48" s="37" t="n"/>
     </row>
     <row r="49">
       <c r="A49" s="14" t="n">
@@ -7204,20 +7250,20 @@
           <t>▌塑料管-通用 (2 项)</t>
         </is>
       </c>
-      <c r="B53" s="19" t="n"/>
-      <c r="C53" s="19" t="n"/>
-      <c r="D53" s="19" t="n"/>
-      <c r="E53" s="19" t="n"/>
-      <c r="F53" s="19" t="n"/>
-      <c r="G53" s="19" t="n"/>
-      <c r="H53" s="19" t="n"/>
-      <c r="I53" s="19" t="n"/>
-      <c r="J53" s="19" t="n"/>
-      <c r="K53" s="19" t="n"/>
-      <c r="L53" s="19" t="n"/>
-      <c r="M53" s="19" t="n"/>
-      <c r="N53" s="19" t="n"/>
-      <c r="O53" s="19" t="n"/>
+      <c r="B53" s="36" t="n"/>
+      <c r="C53" s="36" t="n"/>
+      <c r="D53" s="36" t="n"/>
+      <c r="E53" s="36" t="n"/>
+      <c r="F53" s="36" t="n"/>
+      <c r="G53" s="36" t="n"/>
+      <c r="H53" s="36" t="n"/>
+      <c r="I53" s="36" t="n"/>
+      <c r="J53" s="36" t="n"/>
+      <c r="K53" s="36" t="n"/>
+      <c r="L53" s="36" t="n"/>
+      <c r="M53" s="36" t="n"/>
+      <c r="N53" s="36" t="n"/>
+      <c r="O53" s="37" t="n"/>
     </row>
     <row r="54">
       <c r="A54" s="14" t="n">
@@ -7363,20 +7409,20 @@
           <t>▌原材料-树脂 (2 项)</t>
         </is>
       </c>
-      <c r="B57" s="19" t="n"/>
-      <c r="C57" s="19" t="n"/>
-      <c r="D57" s="19" t="n"/>
-      <c r="E57" s="19" t="n"/>
-      <c r="F57" s="19" t="n"/>
-      <c r="G57" s="19" t="n"/>
-      <c r="H57" s="19" t="n"/>
-      <c r="I57" s="19" t="n"/>
-      <c r="J57" s="19" t="n"/>
-      <c r="K57" s="19" t="n"/>
-      <c r="L57" s="19" t="n"/>
-      <c r="M57" s="19" t="n"/>
-      <c r="N57" s="19" t="n"/>
-      <c r="O57" s="19" t="n"/>
+      <c r="B57" s="36" t="n"/>
+      <c r="C57" s="36" t="n"/>
+      <c r="D57" s="36" t="n"/>
+      <c r="E57" s="36" t="n"/>
+      <c r="F57" s="36" t="n"/>
+      <c r="G57" s="36" t="n"/>
+      <c r="H57" s="36" t="n"/>
+      <c r="I57" s="36" t="n"/>
+      <c r="J57" s="36" t="n"/>
+      <c r="K57" s="36" t="n"/>
+      <c r="L57" s="36" t="n"/>
+      <c r="M57" s="36" t="n"/>
+      <c r="N57" s="36" t="n"/>
+      <c r="O57" s="37" t="n"/>
     </row>
     <row r="58">
       <c r="A58" s="14" t="n">
@@ -7518,20 +7564,20 @@
           <t>▌原材料-纤维 (1 项)</t>
         </is>
       </c>
-      <c r="B61" s="19" t="n"/>
-      <c r="C61" s="19" t="n"/>
-      <c r="D61" s="19" t="n"/>
-      <c r="E61" s="19" t="n"/>
-      <c r="F61" s="19" t="n"/>
-      <c r="G61" s="19" t="n"/>
-      <c r="H61" s="19" t="n"/>
-      <c r="I61" s="19" t="n"/>
-      <c r="J61" s="19" t="n"/>
-      <c r="K61" s="19" t="n"/>
-      <c r="L61" s="19" t="n"/>
-      <c r="M61" s="19" t="n"/>
-      <c r="N61" s="19" t="n"/>
-      <c r="O61" s="19" t="n"/>
+      <c r="B61" s="36" t="n"/>
+      <c r="C61" s="36" t="n"/>
+      <c r="D61" s="36" t="n"/>
+      <c r="E61" s="36" t="n"/>
+      <c r="F61" s="36" t="n"/>
+      <c r="G61" s="36" t="n"/>
+      <c r="H61" s="36" t="n"/>
+      <c r="I61" s="36" t="n"/>
+      <c r="J61" s="36" t="n"/>
+      <c r="K61" s="36" t="n"/>
+      <c r="L61" s="36" t="n"/>
+      <c r="M61" s="36" t="n"/>
+      <c r="N61" s="36" t="n"/>
+      <c r="O61" s="37" t="n"/>
     </row>
     <row r="62">
       <c r="A62" s="14" t="n">
@@ -7604,20 +7650,20 @@
           <t>▌原材料-复合材料 (1 项)</t>
         </is>
       </c>
-      <c r="B64" s="19" t="n"/>
-      <c r="C64" s="19" t="n"/>
-      <c r="D64" s="19" t="n"/>
-      <c r="E64" s="19" t="n"/>
-      <c r="F64" s="19" t="n"/>
-      <c r="G64" s="19" t="n"/>
-      <c r="H64" s="19" t="n"/>
-      <c r="I64" s="19" t="n"/>
-      <c r="J64" s="19" t="n"/>
-      <c r="K64" s="19" t="n"/>
-      <c r="L64" s="19" t="n"/>
-      <c r="M64" s="19" t="n"/>
-      <c r="N64" s="19" t="n"/>
-      <c r="O64" s="19" t="n"/>
+      <c r="B64" s="36" t="n"/>
+      <c r="C64" s="36" t="n"/>
+      <c r="D64" s="36" t="n"/>
+      <c r="E64" s="36" t="n"/>
+      <c r="F64" s="36" t="n"/>
+      <c r="G64" s="36" t="n"/>
+      <c r="H64" s="36" t="n"/>
+      <c r="I64" s="36" t="n"/>
+      <c r="J64" s="36" t="n"/>
+      <c r="K64" s="36" t="n"/>
+      <c r="L64" s="36" t="n"/>
+      <c r="M64" s="36" t="n"/>
+      <c r="N64" s="36" t="n"/>
+      <c r="O64" s="37" t="n"/>
     </row>
     <row r="65">
       <c r="A65" s="14" t="n">
@@ -7690,20 +7736,20 @@
           <t>▌通用-质量体系 (3 项)</t>
         </is>
       </c>
-      <c r="B67" s="19" t="n"/>
-      <c r="C67" s="19" t="n"/>
-      <c r="D67" s="19" t="n"/>
-      <c r="E67" s="19" t="n"/>
-      <c r="F67" s="19" t="n"/>
-      <c r="G67" s="19" t="n"/>
-      <c r="H67" s="19" t="n"/>
-      <c r="I67" s="19" t="n"/>
-      <c r="J67" s="19" t="n"/>
-      <c r="K67" s="19" t="n"/>
-      <c r="L67" s="19" t="n"/>
-      <c r="M67" s="19" t="n"/>
-      <c r="N67" s="19" t="n"/>
-      <c r="O67" s="19" t="n"/>
+      <c r="B67" s="36" t="n"/>
+      <c r="C67" s="36" t="n"/>
+      <c r="D67" s="36" t="n"/>
+      <c r="E67" s="36" t="n"/>
+      <c r="F67" s="36" t="n"/>
+      <c r="G67" s="36" t="n"/>
+      <c r="H67" s="36" t="n"/>
+      <c r="I67" s="36" t="n"/>
+      <c r="J67" s="36" t="n"/>
+      <c r="K67" s="36" t="n"/>
+      <c r="L67" s="36" t="n"/>
+      <c r="M67" s="36" t="n"/>
+      <c r="N67" s="36" t="n"/>
+      <c r="O67" s="37" t="n"/>
     </row>
     <row r="68">
       <c r="A68" s="14" t="n">
@@ -8036,20 +8082,20 @@
           <t>▌产品规范 (23 项)</t>
         </is>
       </c>
-      <c r="B2" s="19" t="n"/>
-      <c r="C2" s="19" t="n"/>
-      <c r="D2" s="19" t="n"/>
-      <c r="E2" s="19" t="n"/>
-      <c r="F2" s="19" t="n"/>
-      <c r="G2" s="19" t="n"/>
-      <c r="H2" s="19" t="n"/>
-      <c r="I2" s="19" t="n"/>
-      <c r="J2" s="19" t="n"/>
-      <c r="K2" s="19" t="n"/>
-      <c r="L2" s="19" t="n"/>
-      <c r="M2" s="19" t="n"/>
-      <c r="N2" s="19" t="n"/>
-      <c r="O2" s="19" t="n"/>
+      <c r="B2" s="36" t="n"/>
+      <c r="C2" s="36" t="n"/>
+      <c r="D2" s="36" t="n"/>
+      <c r="E2" s="36" t="n"/>
+      <c r="F2" s="36" t="n"/>
+      <c r="G2" s="36" t="n"/>
+      <c r="H2" s="36" t="n"/>
+      <c r="I2" s="36" t="n"/>
+      <c r="J2" s="36" t="n"/>
+      <c r="K2" s="36" t="n"/>
+      <c r="L2" s="36" t="n"/>
+      <c r="M2" s="36" t="n"/>
+      <c r="N2" s="36" t="n"/>
+      <c r="O2" s="37" t="n"/>
     </row>
     <row r="3">
       <c r="A3" s="14" t="n">
@@ -9640,20 +9686,20 @@
           <t>▌力学性能 (7 项)</t>
         </is>
       </c>
-      <c r="B27" s="19" t="n"/>
-      <c r="C27" s="19" t="n"/>
-      <c r="D27" s="19" t="n"/>
-      <c r="E27" s="19" t="n"/>
-      <c r="F27" s="19" t="n"/>
-      <c r="G27" s="19" t="n"/>
-      <c r="H27" s="19" t="n"/>
-      <c r="I27" s="19" t="n"/>
-      <c r="J27" s="19" t="n"/>
-      <c r="K27" s="19" t="n"/>
-      <c r="L27" s="19" t="n"/>
-      <c r="M27" s="19" t="n"/>
-      <c r="N27" s="19" t="n"/>
-      <c r="O27" s="19" t="n"/>
+      <c r="B27" s="36" t="n"/>
+      <c r="C27" s="36" t="n"/>
+      <c r="D27" s="36" t="n"/>
+      <c r="E27" s="36" t="n"/>
+      <c r="F27" s="36" t="n"/>
+      <c r="G27" s="36" t="n"/>
+      <c r="H27" s="36" t="n"/>
+      <c r="I27" s="36" t="n"/>
+      <c r="J27" s="36" t="n"/>
+      <c r="K27" s="36" t="n"/>
+      <c r="L27" s="36" t="n"/>
+      <c r="M27" s="36" t="n"/>
+      <c r="N27" s="36" t="n"/>
+      <c r="O27" s="37" t="n"/>
     </row>
     <row r="28">
       <c r="A28" s="14" t="n">
@@ -10140,20 +10186,20 @@
           <t>▌物理性能 (1 项)</t>
         </is>
       </c>
-      <c r="B36" s="19" t="n"/>
-      <c r="C36" s="19" t="n"/>
-      <c r="D36" s="19" t="n"/>
-      <c r="E36" s="19" t="n"/>
-      <c r="F36" s="19" t="n"/>
-      <c r="G36" s="19" t="n"/>
-      <c r="H36" s="19" t="n"/>
-      <c r="I36" s="19" t="n"/>
-      <c r="J36" s="19" t="n"/>
-      <c r="K36" s="19" t="n"/>
-      <c r="L36" s="19" t="n"/>
-      <c r="M36" s="19" t="n"/>
-      <c r="N36" s="19" t="n"/>
-      <c r="O36" s="19" t="n"/>
+      <c r="B36" s="36" t="n"/>
+      <c r="C36" s="36" t="n"/>
+      <c r="D36" s="36" t="n"/>
+      <c r="E36" s="36" t="n"/>
+      <c r="F36" s="36" t="n"/>
+      <c r="G36" s="36" t="n"/>
+      <c r="H36" s="36" t="n"/>
+      <c r="I36" s="36" t="n"/>
+      <c r="J36" s="36" t="n"/>
+      <c r="K36" s="36" t="n"/>
+      <c r="L36" s="36" t="n"/>
+      <c r="M36" s="36" t="n"/>
+      <c r="N36" s="36" t="n"/>
+      <c r="O36" s="37" t="n"/>
     </row>
     <row r="37">
       <c r="A37" s="14" t="n">
@@ -10222,20 +10268,20 @@
           <t>▌化学性能 (4 项)</t>
         </is>
       </c>
-      <c r="B39" s="19" t="n"/>
-      <c r="C39" s="19" t="n"/>
-      <c r="D39" s="19" t="n"/>
-      <c r="E39" s="19" t="n"/>
-      <c r="F39" s="19" t="n"/>
-      <c r="G39" s="19" t="n"/>
-      <c r="H39" s="19" t="n"/>
-      <c r="I39" s="19" t="n"/>
-      <c r="J39" s="19" t="n"/>
-      <c r="K39" s="19" t="n"/>
-      <c r="L39" s="19" t="n"/>
-      <c r="M39" s="19" t="n"/>
-      <c r="N39" s="19" t="n"/>
-      <c r="O39" s="19" t="n"/>
+      <c r="B39" s="36" t="n"/>
+      <c r="C39" s="36" t="n"/>
+      <c r="D39" s="36" t="n"/>
+      <c r="E39" s="36" t="n"/>
+      <c r="F39" s="36" t="n"/>
+      <c r="G39" s="36" t="n"/>
+      <c r="H39" s="36" t="n"/>
+      <c r="I39" s="36" t="n"/>
+      <c r="J39" s="36" t="n"/>
+      <c r="K39" s="36" t="n"/>
+      <c r="L39" s="36" t="n"/>
+      <c r="M39" s="36" t="n"/>
+      <c r="N39" s="36" t="n"/>
+      <c r="O39" s="37" t="n"/>
     </row>
     <row r="40">
       <c r="A40" s="14" t="n">
@@ -10507,20 +10553,20 @@
           <t>▌尺寸测量 (3 项)</t>
         </is>
       </c>
-      <c r="B45" s="19" t="n"/>
-      <c r="C45" s="19" t="n"/>
-      <c r="D45" s="19" t="n"/>
-      <c r="E45" s="19" t="n"/>
-      <c r="F45" s="19" t="n"/>
-      <c r="G45" s="19" t="n"/>
-      <c r="H45" s="19" t="n"/>
-      <c r="I45" s="19" t="n"/>
-      <c r="J45" s="19" t="n"/>
-      <c r="K45" s="19" t="n"/>
-      <c r="L45" s="19" t="n"/>
-      <c r="M45" s="19" t="n"/>
-      <c r="N45" s="19" t="n"/>
-      <c r="O45" s="19" t="n"/>
+      <c r="B45" s="36" t="n"/>
+      <c r="C45" s="36" t="n"/>
+      <c r="D45" s="36" t="n"/>
+      <c r="E45" s="36" t="n"/>
+      <c r="F45" s="36" t="n"/>
+      <c r="G45" s="36" t="n"/>
+      <c r="H45" s="36" t="n"/>
+      <c r="I45" s="36" t="n"/>
+      <c r="J45" s="36" t="n"/>
+      <c r="K45" s="36" t="n"/>
+      <c r="L45" s="36" t="n"/>
+      <c r="M45" s="36" t="n"/>
+      <c r="N45" s="36" t="n"/>
+      <c r="O45" s="37" t="n"/>
     </row>
     <row r="46">
       <c r="A46" s="14" t="n">
@@ -10735,20 +10781,20 @@
           <t>▌无损检测 (1 项)</t>
         </is>
       </c>
-      <c r="B50" s="19" t="n"/>
-      <c r="C50" s="19" t="n"/>
-      <c r="D50" s="19" t="n"/>
-      <c r="E50" s="19" t="n"/>
-      <c r="F50" s="19" t="n"/>
-      <c r="G50" s="19" t="n"/>
-      <c r="H50" s="19" t="n"/>
-      <c r="I50" s="19" t="n"/>
-      <c r="J50" s="19" t="n"/>
-      <c r="K50" s="19" t="n"/>
-      <c r="L50" s="19" t="n"/>
-      <c r="M50" s="19" t="n"/>
-      <c r="N50" s="19" t="n"/>
-      <c r="O50" s="19" t="n"/>
+      <c r="B50" s="36" t="n"/>
+      <c r="C50" s="36" t="n"/>
+      <c r="D50" s="36" t="n"/>
+      <c r="E50" s="36" t="n"/>
+      <c r="F50" s="36" t="n"/>
+      <c r="G50" s="36" t="n"/>
+      <c r="H50" s="36" t="n"/>
+      <c r="I50" s="36" t="n"/>
+      <c r="J50" s="36" t="n"/>
+      <c r="K50" s="36" t="n"/>
+      <c r="L50" s="36" t="n"/>
+      <c r="M50" s="36" t="n"/>
+      <c r="N50" s="36" t="n"/>
+      <c r="O50" s="37" t="n"/>
     </row>
     <row r="51">
       <c r="A51" s="14" t="n">
@@ -10825,20 +10871,20 @@
           <t>▌安装与维护 (5 项)</t>
         </is>
       </c>
-      <c r="B53" s="19" t="n"/>
-      <c r="C53" s="19" t="n"/>
-      <c r="D53" s="19" t="n"/>
-      <c r="E53" s="19" t="n"/>
-      <c r="F53" s="19" t="n"/>
-      <c r="G53" s="19" t="n"/>
-      <c r="H53" s="19" t="n"/>
-      <c r="I53" s="19" t="n"/>
-      <c r="J53" s="19" t="n"/>
-      <c r="K53" s="19" t="n"/>
-      <c r="L53" s="19" t="n"/>
-      <c r="M53" s="19" t="n"/>
-      <c r="N53" s="19" t="n"/>
-      <c r="O53" s="19" t="n"/>
+      <c r="B53" s="36" t="n"/>
+      <c r="C53" s="36" t="n"/>
+      <c r="D53" s="36" t="n"/>
+      <c r="E53" s="36" t="n"/>
+      <c r="F53" s="36" t="n"/>
+      <c r="G53" s="36" t="n"/>
+      <c r="H53" s="36" t="n"/>
+      <c r="I53" s="36" t="n"/>
+      <c r="J53" s="36" t="n"/>
+      <c r="K53" s="36" t="n"/>
+      <c r="L53" s="36" t="n"/>
+      <c r="M53" s="36" t="n"/>
+      <c r="N53" s="36" t="n"/>
+      <c r="O53" s="37" t="n"/>
     </row>
     <row r="54">
       <c r="A54" s="14" t="n">
@@ -11199,20 +11245,20 @@
           <t>▌质量管理 (4 项)</t>
         </is>
       </c>
-      <c r="B60" s="19" t="n"/>
-      <c r="C60" s="19" t="n"/>
-      <c r="D60" s="19" t="n"/>
-      <c r="E60" s="19" t="n"/>
-      <c r="F60" s="19" t="n"/>
-      <c r="G60" s="19" t="n"/>
-      <c r="H60" s="19" t="n"/>
-      <c r="I60" s="19" t="n"/>
-      <c r="J60" s="19" t="n"/>
-      <c r="K60" s="19" t="n"/>
-      <c r="L60" s="19" t="n"/>
-      <c r="M60" s="19" t="n"/>
-      <c r="N60" s="19" t="n"/>
-      <c r="O60" s="19" t="n"/>
+      <c r="B60" s="36" t="n"/>
+      <c r="C60" s="36" t="n"/>
+      <c r="D60" s="36" t="n"/>
+      <c r="E60" s="36" t="n"/>
+      <c r="F60" s="36" t="n"/>
+      <c r="G60" s="36" t="n"/>
+      <c r="H60" s="36" t="n"/>
+      <c r="I60" s="36" t="n"/>
+      <c r="J60" s="36" t="n"/>
+      <c r="K60" s="36" t="n"/>
+      <c r="L60" s="36" t="n"/>
+      <c r="M60" s="36" t="n"/>
+      <c r="N60" s="36" t="n"/>
+      <c r="O60" s="37" t="n"/>
     </row>
     <row r="61">
       <c r="A61" s="14" t="n">
